--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I686"/>
+  <dimension ref="A1:I687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23076,6 +23076,39 @@
       <c r="I686" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>437.85</v>
+      </c>
+      <c r="C687" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="D687" t="n">
+        <v>335.34</v>
+      </c>
+      <c r="E687" t="n">
+        <v>309.09</v>
+      </c>
+      <c r="F687" t="n">
+        <v>319.65</v>
+      </c>
+      <c r="G687" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="H687" t="n">
+        <v>318.33</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23090,7 +23123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30293,6 +30326,16 @@
       </c>
       <c r="B720" t="n">
         <v>0.64</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -30461,28 +30504,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.193728834834429</v>
+        <v>1.191264498574027</v>
       </c>
       <c r="J2" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K2" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02704989456827012</v>
+        <v>0.02702952387740587</v>
       </c>
       <c r="M2" t="n">
-        <v>45.12875225097487</v>
+        <v>45.0753829595542</v>
       </c>
       <c r="N2" t="n">
-        <v>2733.925396896273</v>
+        <v>2730.023901157449</v>
       </c>
       <c r="O2" t="n">
-        <v>52.28695245370754</v>
+        <v>52.24963063178006</v>
       </c>
       <c r="P2" t="n">
-        <v>414.593590432931</v>
+        <v>414.6190664764767</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30543,28 +30586,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007028753593121643</v>
+        <v>0.007373212959636625</v>
       </c>
       <c r="J3" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K3" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002611790468550756</v>
+        <v>0.0002883167890646021</v>
       </c>
       <c r="M3" t="n">
-        <v>2.397627742942815</v>
+        <v>2.395631705928495</v>
       </c>
       <c r="N3" t="n">
-        <v>10.18318777486695</v>
+        <v>10.17023509608905</v>
       </c>
       <c r="O3" t="n">
-        <v>3.191110743121735</v>
+        <v>3.189080603573553</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4184924087738</v>
+        <v>322.4149558115621</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30625,28 +30668,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2837638009174508</v>
+        <v>0.283491305238701</v>
       </c>
       <c r="J4" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K4" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3042295901546547</v>
+        <v>0.3045127637287103</v>
       </c>
       <c r="M4" t="n">
-        <v>2.205426264731996</v>
+        <v>2.203662432835209</v>
       </c>
       <c r="N4" t="n">
-        <v>9.916476317668145</v>
+        <v>9.903204608488121</v>
       </c>
       <c r="O4" t="n">
-        <v>3.149043714791547</v>
+        <v>3.146935749024457</v>
       </c>
       <c r="P4" t="n">
-        <v>328.7940385949826</v>
+        <v>328.7968363341396</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30707,28 +30750,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01895365956943255</v>
+        <v>0.01951508000157586</v>
       </c>
       <c r="J5" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K5" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001037748218996382</v>
+        <v>0.001103488582046452</v>
       </c>
       <c r="M5" t="n">
-        <v>3.236028319731057</v>
+        <v>3.234155919903073</v>
       </c>
       <c r="N5" t="n">
-        <v>18.62181997711584</v>
+        <v>18.59969944224283</v>
       </c>
       <c r="O5" t="n">
-        <v>4.315300682121217</v>
+        <v>4.312736885348193</v>
       </c>
       <c r="P5" t="n">
-        <v>306.726055617308</v>
+        <v>306.7202914601157</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30785,28 +30828,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05078359141727389</v>
+        <v>0.05188968216574842</v>
       </c>
       <c r="J6" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K6" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005992593225065623</v>
+        <v>0.006270579451324587</v>
       </c>
       <c r="M6" t="n">
-        <v>3.472985769997208</v>
+        <v>3.47371151621437</v>
       </c>
       <c r="N6" t="n">
-        <v>23.03565335517851</v>
+        <v>23.02157837423122</v>
       </c>
       <c r="O6" t="n">
-        <v>4.799547203140991</v>
+        <v>4.798080696927806</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6455649372144</v>
+        <v>314.6342085978687</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30863,28 +30906,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04740724330768234</v>
+        <v>0.04816216006246303</v>
       </c>
       <c r="J7" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K7" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006085612471949942</v>
+        <v>0.006297981433406319</v>
       </c>
       <c r="M7" t="n">
-        <v>3.192896789805327</v>
+        <v>3.192031452191872</v>
       </c>
       <c r="N7" t="n">
-        <v>19.76573550256195</v>
+        <v>19.74600811927948</v>
       </c>
       <c r="O7" t="n">
-        <v>4.445867238521856</v>
+        <v>4.443648064291263</v>
       </c>
       <c r="P7" t="n">
-        <v>313.7989599489223</v>
+        <v>313.7912091465068</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30941,28 +30984,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01646575033686314</v>
+        <v>0.01753061640378864</v>
       </c>
       <c r="J8" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K8" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008034561540766205</v>
+        <v>0.0009128100112040238</v>
       </c>
       <c r="M8" t="n">
-        <v>3.100012054575789</v>
+        <v>3.100544879898234</v>
       </c>
       <c r="N8" t="n">
-        <v>18.15643941838214</v>
+        <v>18.14805018467884</v>
       </c>
       <c r="O8" t="n">
-        <v>4.261037364114769</v>
+        <v>4.260052838249644</v>
       </c>
       <c r="P8" t="n">
-        <v>314.3718912363148</v>
+        <v>314.3609581547115</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31000,7 +31043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I686"/>
+  <dimension ref="A1:I687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63237,6 +63280,53 @@
         </is>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-43.580363704276145,172.7773922436346</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-43.581124021896535,172.77608887922202</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-43.5817702721576,172.7763359055985</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-43.582475158089615,172.77637295798073</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-43.58305826278332,172.77687494013875</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-43.58361801976978,172.77740008881938</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-43.58412226305154,172.7779841847965</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I687"/>
+  <dimension ref="A1:I688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23107,6 +23107,39 @@
         <v>318.33</v>
       </c>
       <c r="I687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>447.68</v>
+      </c>
+      <c r="C688" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="D688" t="n">
+        <v>335.22</v>
+      </c>
+      <c r="E688" t="n">
+        <v>307.73</v>
+      </c>
+      <c r="F688" t="n">
+        <v>317.8</v>
+      </c>
+      <c r="G688" t="n">
+        <v>315.64</v>
+      </c>
+      <c r="H688" t="n">
+        <v>316.53</v>
+      </c>
+      <c r="I688" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23123,7 +23156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B721"/>
+  <dimension ref="A1:B722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30336,6 +30369,16 @@
       </c>
       <c r="B721" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -30504,28 +30547,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.191264498574027</v>
+        <v>1.191780117329546</v>
       </c>
       <c r="J2" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K2" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02702952387740587</v>
+        <v>0.02714216866986507</v>
       </c>
       <c r="M2" t="n">
-        <v>45.0753829595542</v>
+        <v>45.01188041386837</v>
       </c>
       <c r="N2" t="n">
-        <v>2730.023901157449</v>
+        <v>2726.042631732329</v>
       </c>
       <c r="O2" t="n">
-        <v>52.24963063178006</v>
+        <v>52.21151819026458</v>
       </c>
       <c r="P2" t="n">
-        <v>414.6190664764767</v>
+        <v>414.6137221127035</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30586,28 +30629,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007373212959636625</v>
+        <v>0.007582150325820642</v>
       </c>
       <c r="J3" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K3" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002883167890646021</v>
+        <v>0.000305899226135331</v>
       </c>
       <c r="M3" t="n">
-        <v>2.395631705928495</v>
+        <v>2.39304740226019</v>
       </c>
       <c r="N3" t="n">
-        <v>10.17023509608905</v>
+        <v>10.15612513319422</v>
       </c>
       <c r="O3" t="n">
-        <v>3.189080603573553</v>
+        <v>3.186867605218991</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4149558115621</v>
+        <v>322.4128049688509</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30668,28 +30711,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.283491305238701</v>
+        <v>0.2831764791702112</v>
       </c>
       <c r="J4" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K4" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3045127637287103</v>
+        <v>0.3047274788827096</v>
       </c>
       <c r="M4" t="n">
-        <v>2.203662432835209</v>
+        <v>2.20213530019246</v>
       </c>
       <c r="N4" t="n">
-        <v>9.903204608488121</v>
+        <v>9.890364856745798</v>
       </c>
       <c r="O4" t="n">
-        <v>3.146935749024457</v>
+        <v>3.144895047016004</v>
       </c>
       <c r="P4" t="n">
-        <v>328.7968363341396</v>
+        <v>328.8000772161661</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30750,28 +30793,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01951508000157586</v>
+        <v>0.01966426252265873</v>
       </c>
       <c r="J5" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K5" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001103488582046452</v>
+        <v>0.001124190101698175</v>
       </c>
       <c r="M5" t="n">
-        <v>3.234155919903073</v>
+        <v>3.230199060968692</v>
       </c>
       <c r="N5" t="n">
-        <v>18.59969944224283</v>
+        <v>18.57297938337476</v>
       </c>
       <c r="O5" t="n">
-        <v>4.312736885348193</v>
+        <v>4.309637964304515</v>
       </c>
       <c r="P5" t="n">
-        <v>306.7202914601157</v>
+        <v>306.7187557456384</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30828,28 +30871,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05188968216574842</v>
+        <v>0.05243404827631678</v>
       </c>
       <c r="J6" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K6" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006270579451324587</v>
+        <v>0.006422315982776539</v>
       </c>
       <c r="M6" t="n">
-        <v>3.47371151621437</v>
+        <v>3.471484155403974</v>
       </c>
       <c r="N6" t="n">
-        <v>23.02157837423122</v>
+        <v>22.99277816702753</v>
       </c>
       <c r="O6" t="n">
-        <v>4.798080696927806</v>
+        <v>4.795078536064611</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6342085978687</v>
+        <v>314.6286047850967</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30906,28 +30949,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04816216006246303</v>
+        <v>0.04833892184194476</v>
       </c>
       <c r="J7" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K7" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006297981433406319</v>
+        <v>0.006365280694994868</v>
       </c>
       <c r="M7" t="n">
-        <v>3.192031452191872</v>
+        <v>3.188267186514714</v>
       </c>
       <c r="N7" t="n">
-        <v>19.74600811927948</v>
+        <v>19.71776236953369</v>
       </c>
       <c r="O7" t="n">
-        <v>4.443648064291263</v>
+        <v>4.440468710568029</v>
       </c>
       <c r="P7" t="n">
-        <v>313.7912091465068</v>
+        <v>313.7893895256703</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30984,28 +31027,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01753061640378864</v>
+        <v>0.01804751201139842</v>
       </c>
       <c r="J8" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K8" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009128100112040238</v>
+        <v>0.0009704393891275531</v>
       </c>
       <c r="M8" t="n">
-        <v>3.100544879898234</v>
+        <v>3.098476194616015</v>
       </c>
       <c r="N8" t="n">
-        <v>18.14805018467884</v>
+        <v>18.12588052557654</v>
       </c>
       <c r="O8" t="n">
-        <v>4.260052838249644</v>
+        <v>4.257450002710137</v>
       </c>
       <c r="P8" t="n">
-        <v>314.3609581547115</v>
+        <v>314.3556371287484</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31043,7 +31086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I687"/>
+  <dimension ref="A1:I688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63327,6 +63370,53 @@
         </is>
       </c>
     </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-43.58035390652436,172.7775132482046</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-43.58112447035224,172.7760833397667</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-43.58177053269356,172.77633446311904</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-43.582479879298916,172.7763574149587</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-43.583066518534906,172.77685503761583</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-43.583628487060906,172.77738131723888</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-43.58413251820994,172.77796691971517</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I688"/>
+  <dimension ref="A1:I689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23140,6 +23140,39 @@
         <v>316.53</v>
       </c>
       <c r="I688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>465.34</v>
+      </c>
+      <c r="C689" t="n">
+        <v>323.24</v>
+      </c>
+      <c r="D689" t="n">
+        <v>335.53</v>
+      </c>
+      <c r="E689" t="n">
+        <v>307.16</v>
+      </c>
+      <c r="F689" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="G689" t="n">
+        <v>315.43</v>
+      </c>
+      <c r="H689" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="I689" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23156,7 +23189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30379,6 +30412,16 @@
       </c>
       <c r="B722" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -30547,28 +30590,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.191780117329546</v>
+        <v>1.197650121666603</v>
       </c>
       <c r="J2" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K2" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02714216866986507</v>
+        <v>0.02748873223606207</v>
       </c>
       <c r="M2" t="n">
-        <v>45.01188041386837</v>
+        <v>44.97231582692486</v>
       </c>
       <c r="N2" t="n">
-        <v>2726.042631732329</v>
+        <v>2722.60910732218</v>
       </c>
       <c r="O2" t="n">
-        <v>52.21151819026458</v>
+        <v>52.17862692062891</v>
       </c>
       <c r="P2" t="n">
-        <v>414.6137221127035</v>
+        <v>414.5527698175529</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30629,28 +30672,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007582150325820642</v>
+        <v>0.007772391443880367</v>
       </c>
       <c r="J3" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K3" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000305899226135331</v>
+        <v>0.0003225134225202098</v>
       </c>
       <c r="M3" t="n">
-        <v>2.39304740226019</v>
+        <v>2.390386696381082</v>
       </c>
       <c r="N3" t="n">
-        <v>10.15612513319422</v>
+        <v>10.14193883365842</v>
       </c>
       <c r="O3" t="n">
-        <v>3.186867605218991</v>
+        <v>3.184641083961962</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4128049688509</v>
+        <v>322.4108430188979</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30711,28 +30754,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2831764791702112</v>
+        <v>0.2829551907544123</v>
       </c>
       <c r="J4" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K4" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3047274788827096</v>
+        <v>0.3051000591384238</v>
       </c>
       <c r="M4" t="n">
-        <v>2.20213530019246</v>
+        <v>2.200109686910673</v>
       </c>
       <c r="N4" t="n">
-        <v>9.890364856745798</v>
+        <v>9.876768011134493</v>
       </c>
       <c r="O4" t="n">
-        <v>3.144895047016004</v>
+        <v>3.142732570731161</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8000772161661</v>
+        <v>328.8023593558077</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30793,28 +30836,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01966426252265873</v>
+        <v>0.01964023278832739</v>
       </c>
       <c r="J5" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K5" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001124190101698175</v>
+        <v>0.001125262226772117</v>
       </c>
       <c r="M5" t="n">
-        <v>3.230199060968692</v>
+        <v>3.225614186669985</v>
       </c>
       <c r="N5" t="n">
-        <v>18.57297938337476</v>
+        <v>18.54599295591023</v>
       </c>
       <c r="O5" t="n">
-        <v>4.309637964304515</v>
+        <v>4.306505887132889</v>
       </c>
       <c r="P5" t="n">
-        <v>306.7187557456384</v>
+        <v>306.7190035634425</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30871,28 +30914,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05243404827631678</v>
+        <v>0.05285339792859829</v>
       </c>
       <c r="J6" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K6" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006422315982776539</v>
+        <v>0.006546067185889126</v>
       </c>
       <c r="M6" t="n">
-        <v>3.471484155403974</v>
+        <v>3.468606172216051</v>
       </c>
       <c r="N6" t="n">
-        <v>22.99277816702753</v>
+        <v>22.96215481564255</v>
       </c>
       <c r="O6" t="n">
-        <v>4.795078536064611</v>
+        <v>4.791884265676973</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6286047850967</v>
+        <v>314.6242800468962</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30949,28 +30992,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04833892184194476</v>
+        <v>0.04845015353349244</v>
       </c>
       <c r="J7" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K7" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006365280694994868</v>
+        <v>0.006415997383793171</v>
       </c>
       <c r="M7" t="n">
-        <v>3.188267186514714</v>
+        <v>3.184187011138652</v>
       </c>
       <c r="N7" t="n">
-        <v>19.71776236953369</v>
+        <v>19.68929957514745</v>
       </c>
       <c r="O7" t="n">
-        <v>4.440468710568029</v>
+        <v>4.437262621836513</v>
       </c>
       <c r="P7" t="n">
-        <v>313.7893895256703</v>
+        <v>313.7882423971514</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31027,28 +31070,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01804751201139842</v>
+        <v>0.01846484206437686</v>
       </c>
       <c r="J8" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K8" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009704393891275531</v>
+        <v>0.001019093568938256</v>
       </c>
       <c r="M8" t="n">
-        <v>3.098476194616015</v>
+        <v>3.095942656722504</v>
       </c>
       <c r="N8" t="n">
-        <v>18.12588052557654</v>
+        <v>18.10230428325573</v>
       </c>
       <c r="O8" t="n">
-        <v>4.257450002710137</v>
+        <v>4.254680279792564</v>
       </c>
       <c r="P8" t="n">
-        <v>314.3556371287484</v>
+        <v>314.3513332186044</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31086,7 +31129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I688"/>
+  <dimension ref="A1:I689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63417,6 +63460,53 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:06+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-43.58033630413761,172.7777306378027</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-43.58112453014633,172.77608260117265</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-43.581769859642286,172.77633818952427</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-43.58248185804041,172.77635090060318</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-43.58306830356182,172.77685073436692</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-43.58362963791472,172.77737925334742</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-43.584134284375835,172.7779639462839</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I689"/>
+  <dimension ref="A1:I693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23173,6 +23173,138 @@
         <v>316.22</v>
       </c>
       <c r="I689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>475.99</v>
+      </c>
+      <c r="C690" t="n">
+        <v>323.07</v>
+      </c>
+      <c r="D690" t="n">
+        <v>334.86</v>
+      </c>
+      <c r="E690" t="n">
+        <v>305.85</v>
+      </c>
+      <c r="F690" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="G690" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="H690" t="n">
+        <v>314.8</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>484.85</v>
+      </c>
+      <c r="C691" t="n">
+        <v>322.98</v>
+      </c>
+      <c r="D691" t="n">
+        <v>335.24</v>
+      </c>
+      <c r="E691" t="n">
+        <v>306.16</v>
+      </c>
+      <c r="F691" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="G691" t="n">
+        <v>314.23</v>
+      </c>
+      <c r="H691" t="n">
+        <v>314.84</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:38+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>485.42</v>
+      </c>
+      <c r="C692" t="n">
+        <v>323.02</v>
+      </c>
+      <c r="D692" t="n">
+        <v>334.99</v>
+      </c>
+      <c r="E692" t="n">
+        <v>306.23</v>
+      </c>
+      <c r="F692" t="n">
+        <v>315.14</v>
+      </c>
+      <c r="G692" t="n">
+        <v>314.11</v>
+      </c>
+      <c r="H692" t="n">
+        <v>314.6</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>493.88</v>
+      </c>
+      <c r="C693" t="n">
+        <v>322.87</v>
+      </c>
+      <c r="D693" t="n">
+        <v>335.39</v>
+      </c>
+      <c r="E693" t="n">
+        <v>306.49</v>
+      </c>
+      <c r="F693" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="G693" t="n">
+        <v>314.06</v>
+      </c>
+      <c r="H693" t="n">
+        <v>314.65</v>
+      </c>
+      <c r="I693" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23189,7 +23321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B723"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30422,6 +30554,46 @@
       </c>
       <c r="B723" t="n">
         <v>0.85</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -30590,28 +30762,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.197650121666603</v>
+        <v>1.244293668443307</v>
       </c>
       <c r="J2" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="K2" t="n">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02748873223606207</v>
+        <v>0.02990708965037359</v>
       </c>
       <c r="M2" t="n">
-        <v>44.97231582692486</v>
+        <v>44.91629941552331</v>
       </c>
       <c r="N2" t="n">
-        <v>2722.60910732218</v>
+        <v>2715.617426333037</v>
       </c>
       <c r="O2" t="n">
-        <v>52.17862692062891</v>
+        <v>52.11158629645654</v>
       </c>
       <c r="P2" t="n">
-        <v>414.5527698175529</v>
+        <v>414.0668004171906</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30672,28 +30844,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007772391443880367</v>
+        <v>0.008210533552742887</v>
       </c>
       <c r="J3" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="K3" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003225134225202098</v>
+        <v>0.0003647749024586755</v>
       </c>
       <c r="M3" t="n">
-        <v>2.390386696381082</v>
+        <v>2.378428866589804</v>
       </c>
       <c r="N3" t="n">
-        <v>10.14193883365842</v>
+        <v>10.08411140764335</v>
       </c>
       <c r="O3" t="n">
-        <v>3.184641083961962</v>
+        <v>3.175548993110223</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4108430188979</v>
+        <v>322.4063105504237</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30754,28 +30926,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2829551907544123</v>
+        <v>0.2815686302386784</v>
       </c>
       <c r="J4" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="K4" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3051000591384238</v>
+        <v>0.3057250303569474</v>
       </c>
       <c r="M4" t="n">
-        <v>2.200109686910673</v>
+        <v>2.194679293436147</v>
       </c>
       <c r="N4" t="n">
-        <v>9.876768011134493</v>
+        <v>9.827596587279183</v>
       </c>
       <c r="O4" t="n">
-        <v>3.142732570731161</v>
+        <v>3.134899773083533</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8023593558077</v>
+        <v>328.8167036353362</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30836,28 +31008,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01964023278832739</v>
+        <v>0.01838133016925667</v>
       </c>
       <c r="J5" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="K5" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001125262226772117</v>
+        <v>0.0009988713949723449</v>
       </c>
       <c r="M5" t="n">
-        <v>3.225614186669985</v>
+        <v>3.212684007929382</v>
       </c>
       <c r="N5" t="n">
-        <v>18.54599295591023</v>
+        <v>18.44541997387737</v>
       </c>
       <c r="O5" t="n">
-        <v>4.306505887132889</v>
+        <v>4.294813147725681</v>
       </c>
       <c r="P5" t="n">
-        <v>306.7190035634425</v>
+        <v>306.7320259978322</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30914,28 +31086,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05285339792859829</v>
+        <v>0.05188698084942903</v>
       </c>
       <c r="J6" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="K6" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006546067185889126</v>
+        <v>0.006394989128257533</v>
       </c>
       <c r="M6" t="n">
-        <v>3.468606172216051</v>
+        <v>3.452818817817315</v>
       </c>
       <c r="N6" t="n">
-        <v>22.96215481564255</v>
+        <v>22.83331867906235</v>
       </c>
       <c r="O6" t="n">
-        <v>4.791884265676973</v>
+        <v>4.778422195564384</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6242800468962</v>
+        <v>314.6342806628226</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30992,28 +31164,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04845015353349244</v>
+        <v>0.04727634456034846</v>
       </c>
       <c r="J7" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="K7" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006415997383793171</v>
+        <v>0.00619202141472508</v>
       </c>
       <c r="M7" t="n">
-        <v>3.184187011138652</v>
+        <v>3.171201659953904</v>
       </c>
       <c r="N7" t="n">
-        <v>19.68929957514745</v>
+        <v>19.58105472275852</v>
       </c>
       <c r="O7" t="n">
-        <v>4.437262621836513</v>
+        <v>4.425048555977496</v>
       </c>
       <c r="P7" t="n">
-        <v>313.7882423971514</v>
+        <v>313.8003868963386</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31070,28 +31242,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01846484206437686</v>
+        <v>0.01832691564312815</v>
       </c>
       <c r="J8" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="K8" t="n">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001019093568938256</v>
+        <v>0.001017642813443742</v>
       </c>
       <c r="M8" t="n">
-        <v>3.095942656722504</v>
+        <v>3.078729149097659</v>
       </c>
       <c r="N8" t="n">
-        <v>18.10230428325573</v>
+        <v>17.99780256443686</v>
       </c>
       <c r="O8" t="n">
-        <v>4.254680279792564</v>
+        <v>4.242381708950393</v>
       </c>
       <c r="P8" t="n">
-        <v>314.3513332186044</v>
+        <v>314.352761300559</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31129,7 +31301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I689"/>
+  <dimension ref="A1:I693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63507,6 +63679,194 @@
         </is>
       </c>
     </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-43.58032568868177,172.77786173622587</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-43.58112469956284,172.77608050848949</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-43.58177131430135,172.77633013568055</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-43.58248640567298,172.77633592901253</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-43.583076782437416,172.7768302939311</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-43.58363780349542,172.77736460954398</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-43.584142374554126,172.77795032604814</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-43.58031685730527,172.77797080023151</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-43.58112478925393,172.7760794005984</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-43.5817704892709,172.77633470353229</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-43.58248532951583,172.77633947190822</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-43.58307856746339,172.77682599068072</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-43.58363621422147,172.7773674596805</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>-43.58414214666181,172.7779507097168</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:38+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-43.58031628914318,172.77797781676352</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-43.58112474939122,172.77607989299443</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-43.58177103205411,172.7763316983667</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-43.58248508651259,172.77634027191692</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-43.5830783889608,172.77682642100578</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-43.58363687185207,172.7773662803137</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>-43.58414351401573,172.77794840770483</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-43.58030785637084,172.778081956855</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-43.581124898876354,172.77607804650927</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-43.58177016360093,172.7763365066316</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-43.582484183929076,172.7763432433777</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-43.58307856746339,172.77682599068072</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-43.58363714586483,172.77736578891083</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>-43.58414322915033,172.77794888729065</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I693"/>
+  <dimension ref="A1:I695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23305,6 +23305,72 @@
         <v>314.65</v>
       </c>
       <c r="I693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>493.62</v>
+      </c>
+      <c r="C694" t="n">
+        <v>321.88</v>
+      </c>
+      <c r="D694" t="n">
+        <v>334.77</v>
+      </c>
+      <c r="E694" t="n">
+        <v>305.19</v>
+      </c>
+      <c r="F694" t="n">
+        <v>313.79</v>
+      </c>
+      <c r="G694" t="n">
+        <v>313.64</v>
+      </c>
+      <c r="H694" t="n">
+        <v>314.29</v>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>493.68</v>
+      </c>
+      <c r="C695" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="D695" t="n">
+        <v>334.66</v>
+      </c>
+      <c r="E695" t="n">
+        <v>305.17</v>
+      </c>
+      <c r="F695" t="n">
+        <v>313.74</v>
+      </c>
+      <c r="G695" t="n">
+        <v>313.37</v>
+      </c>
+      <c r="H695" t="n">
+        <v>314.16</v>
+      </c>
+      <c r="I695" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23321,7 +23387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30594,6 +30660,26 @@
       </c>
       <c r="B727" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -30762,28 +30848,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.244293668443307</v>
+        <v>1.272194229505031</v>
       </c>
       <c r="J2" t="n">
+        <v>694</v>
+      </c>
+      <c r="K2" t="n">
         <v>692</v>
       </c>
-      <c r="K2" t="n">
-        <v>690</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.02990708965037359</v>
+        <v>0.03135713974334398</v>
       </c>
       <c r="M2" t="n">
-        <v>44.91629941552331</v>
+        <v>44.90830268488024</v>
       </c>
       <c r="N2" t="n">
-        <v>2715.617426333037</v>
+        <v>2713.977982915313</v>
       </c>
       <c r="O2" t="n">
-        <v>52.11158629645654</v>
+        <v>52.09585379773819</v>
       </c>
       <c r="P2" t="n">
-        <v>414.0668004171906</v>
+        <v>413.7752497281504</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30844,28 +30930,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008210533552742887</v>
+        <v>0.00778137591531223</v>
       </c>
       <c r="J3" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K3" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003647749024586755</v>
+        <v>0.0003298208481401499</v>
       </c>
       <c r="M3" t="n">
-        <v>2.378428866589804</v>
+        <v>2.373895822698133</v>
       </c>
       <c r="N3" t="n">
-        <v>10.08411140764335</v>
+        <v>10.05654211515787</v>
       </c>
       <c r="O3" t="n">
-        <v>3.175548993110223</v>
+        <v>3.171205151855974</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4063105504237</v>
+        <v>322.4107647767941</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30926,28 +31012,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2815686302386784</v>
+        <v>0.2806359515367263</v>
       </c>
       <c r="J4" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K4" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3057250303569474</v>
+        <v>0.305597130091331</v>
       </c>
       <c r="M4" t="n">
-        <v>2.194679293436147</v>
+        <v>2.193220186990615</v>
       </c>
       <c r="N4" t="n">
-        <v>9.827596587279183</v>
+        <v>9.806320876099331</v>
       </c>
       <c r="O4" t="n">
-        <v>3.134899773083533</v>
+        <v>3.131504570665566</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8167036353362</v>
+        <v>328.8263839458199</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31008,28 +31094,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01838133016925667</v>
+        <v>0.01717016682442048</v>
       </c>
       <c r="J5" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K5" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009988713949723449</v>
+        <v>0.000877020952012586</v>
       </c>
       <c r="M5" t="n">
-        <v>3.212684007929382</v>
+        <v>3.208975945722799</v>
       </c>
       <c r="N5" t="n">
-        <v>18.44541997387737</v>
+        <v>18.40412860028688</v>
       </c>
       <c r="O5" t="n">
-        <v>4.294813147725681</v>
+        <v>4.290003333365474</v>
       </c>
       <c r="P5" t="n">
-        <v>306.7320259978322</v>
+        <v>306.7445966900964</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31086,28 +31172,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05188698084942903</v>
+        <v>0.05055175489514419</v>
       </c>
       <c r="J6" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K6" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006394989128257533</v>
+        <v>0.006109107376226275</v>
       </c>
       <c r="M6" t="n">
-        <v>3.452818817817315</v>
+        <v>3.448706476793235</v>
       </c>
       <c r="N6" t="n">
-        <v>22.83331867906235</v>
+        <v>22.78193858539839</v>
       </c>
       <c r="O6" t="n">
-        <v>4.778422195564384</v>
+        <v>4.773042906301848</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6342806628226</v>
+        <v>314.6481390073185</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31164,28 +31250,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04727634456034846</v>
+        <v>0.04635444635293644</v>
       </c>
       <c r="J7" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K7" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00619202141472508</v>
+        <v>0.005992293561487005</v>
       </c>
       <c r="M7" t="n">
-        <v>3.171201659953904</v>
+        <v>3.166281004116573</v>
       </c>
       <c r="N7" t="n">
-        <v>19.58105472275852</v>
+        <v>19.5315503661291</v>
       </c>
       <c r="O7" t="n">
-        <v>4.425048555977496</v>
+        <v>4.419451364833546</v>
       </c>
       <c r="P7" t="n">
-        <v>313.8003868963386</v>
+        <v>313.8099553417887</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31242,28 +31328,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01832691564312815</v>
+        <v>0.01796424393261464</v>
       </c>
       <c r="J8" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K8" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001017642813443742</v>
+        <v>0.0009843629589604275</v>
       </c>
       <c r="M8" t="n">
-        <v>3.078729149097659</v>
+        <v>3.071617984199789</v>
       </c>
       <c r="N8" t="n">
-        <v>17.99780256443686</v>
+        <v>17.94701233159493</v>
       </c>
       <c r="O8" t="n">
-        <v>4.242381708950393</v>
+        <v>4.236391428042849</v>
       </c>
       <c r="P8" t="n">
-        <v>314.352761300559</v>
+        <v>314.3565255003804</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31301,7 +31387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I693"/>
+  <dimension ref="A1:I695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63867,6 +63953,100 @@
         </is>
       </c>
     </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:13:43+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-43.58030811553547,172.77807875633252</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-43.58112588547742,172.7760658597071</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-43.58177150970326,172.77632905382094</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-43.5824886968459,172.77632838607286</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-43.58308441342233,172.77681189753397</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-43.58363944757184,172.77736166112666</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>-43.58414528018115,172.77794543427245</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-43.58030805572825,172.77807949491464</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-43.581125835649125,172.77606647520216</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-43.58177174852782,172.77632773154804</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-43.582488766275375,172.77632815749894</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-43.583084636550474,172.77681135962757</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-43.58364092724056,172.77735900755098</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>-43.584146020831135,172.77794418734916</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I695"/>
+  <dimension ref="A1:I698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23371,6 +23371,105 @@
         <v>314.16</v>
       </c>
       <c r="I695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>493.6</v>
+      </c>
+      <c r="C696" t="n">
+        <v>321.9</v>
+      </c>
+      <c r="D696" t="n">
+        <v>334.31</v>
+      </c>
+      <c r="E696" t="n">
+        <v>305.22</v>
+      </c>
+      <c r="F696" t="n">
+        <v>313.84</v>
+      </c>
+      <c r="G696" t="n">
+        <v>313.39</v>
+      </c>
+      <c r="H696" t="n">
+        <v>314.17</v>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:34+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>494.04</v>
+      </c>
+      <c r="C697" t="n">
+        <v>320.85</v>
+      </c>
+      <c r="D697" t="n">
+        <v>333.76</v>
+      </c>
+      <c r="E697" t="n">
+        <v>303.69</v>
+      </c>
+      <c r="F697" t="n">
+        <v>312.51</v>
+      </c>
+      <c r="G697" t="n">
+        <v>311.52</v>
+      </c>
+      <c r="H697" t="n">
+        <v>312.68</v>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>494.11</v>
+      </c>
+      <c r="C698" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="D698" t="n">
+        <v>333.12</v>
+      </c>
+      <c r="E698" t="n">
+        <v>303.06</v>
+      </c>
+      <c r="F698" t="n">
+        <v>311.54</v>
+      </c>
+      <c r="G698" t="n">
+        <v>310.53</v>
+      </c>
+      <c r="H698" t="n">
+        <v>311.98</v>
+      </c>
+      <c r="I698" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23387,7 +23486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B729"/>
+  <dimension ref="A1:B732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30680,6 +30779,36 @@
       </c>
       <c r="B729" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -30848,28 +30977,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.272194229505031</v>
+        <v>1.313429301502046</v>
       </c>
       <c r="J2" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K2" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03135713974334398</v>
+        <v>0.03357212865349779</v>
       </c>
       <c r="M2" t="n">
-        <v>44.90830268488024</v>
+        <v>44.8953924936915</v>
       </c>
       <c r="N2" t="n">
-        <v>2713.977982915313</v>
+        <v>2711.391150413494</v>
       </c>
       <c r="O2" t="n">
-        <v>52.09585379773819</v>
+        <v>52.07102025516203</v>
       </c>
       <c r="P2" t="n">
-        <v>413.7752497281504</v>
+        <v>413.3433370865405</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30930,28 +31059,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00778137591531223</v>
+        <v>0.006354789671600304</v>
       </c>
       <c r="J3" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K3" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003298208481401499</v>
+        <v>0.0002219348085752415</v>
       </c>
       <c r="M3" t="n">
-        <v>2.373895822698133</v>
+        <v>2.371329723824507</v>
       </c>
       <c r="N3" t="n">
-        <v>10.05654211515787</v>
+        <v>10.02627154104604</v>
       </c>
       <c r="O3" t="n">
-        <v>3.171205151855974</v>
+        <v>3.166428830882835</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4107647767941</v>
+        <v>322.42561499942</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31012,28 +31141,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2806359515367263</v>
+        <v>0.2783740759581425</v>
       </c>
       <c r="J4" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K4" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L4" t="n">
-        <v>0.305597130091331</v>
+        <v>0.3036770684876194</v>
       </c>
       <c r="M4" t="n">
-        <v>2.193220186990615</v>
+        <v>2.195464207642195</v>
       </c>
       <c r="N4" t="n">
-        <v>9.806320876099331</v>
+        <v>9.792987391099503</v>
       </c>
       <c r="O4" t="n">
-        <v>3.131504570665566</v>
+        <v>3.129374920187657</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8263839458199</v>
+        <v>328.8499226392336</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31094,28 +31223,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01717016682442048</v>
+        <v>0.01433295926198604</v>
       </c>
       <c r="J5" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K5" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000877020952012586</v>
+        <v>0.0006158873719450675</v>
       </c>
       <c r="M5" t="n">
-        <v>3.208975945722799</v>
+        <v>3.208128707452136</v>
       </c>
       <c r="N5" t="n">
-        <v>18.40412860028688</v>
+        <v>18.37222661761517</v>
       </c>
       <c r="O5" t="n">
-        <v>4.290003333365474</v>
+        <v>4.286283543772527</v>
       </c>
       <c r="P5" t="n">
-        <v>306.7445966900964</v>
+        <v>306.7741251451115</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31172,28 +31301,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05055175489514419</v>
+        <v>0.0475796637183807</v>
       </c>
       <c r="J6" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K6" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006109107376226275</v>
+        <v>0.005457782155647739</v>
       </c>
       <c r="M6" t="n">
-        <v>3.448706476793235</v>
+        <v>3.446779683162605</v>
       </c>
       <c r="N6" t="n">
-        <v>22.78193858539839</v>
+        <v>22.73571842054839</v>
       </c>
       <c r="O6" t="n">
-        <v>4.773042906301848</v>
+        <v>4.768198655734511</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6481390073185</v>
+        <v>314.6790720319623</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31250,28 +31379,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04635444635293644</v>
+        <v>0.04350356330415836</v>
       </c>
       <c r="J7" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K7" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005992293561487005</v>
+        <v>0.00532118665734671</v>
       </c>
       <c r="M7" t="n">
-        <v>3.166281004116573</v>
+        <v>3.16589491260052</v>
       </c>
       <c r="N7" t="n">
-        <v>19.5315503661291</v>
+        <v>19.49768073333422</v>
       </c>
       <c r="O7" t="n">
-        <v>4.419451364833546</v>
+        <v>4.415617820116934</v>
       </c>
       <c r="P7" t="n">
-        <v>313.8099553417887</v>
+        <v>313.8396298469081</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31328,28 +31457,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01796424393261464</v>
+        <v>0.01629240889445184</v>
       </c>
       <c r="J8" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="K8" t="n">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009843629589604275</v>
+        <v>0.000817145526239349</v>
       </c>
       <c r="M8" t="n">
-        <v>3.071617984199789</v>
+        <v>3.066482657404197</v>
       </c>
       <c r="N8" t="n">
-        <v>17.94701233159493</v>
+        <v>17.88854785667815</v>
       </c>
       <c r="O8" t="n">
-        <v>4.236391428042849</v>
+        <v>4.22948553096924</v>
       </c>
       <c r="P8" t="n">
-        <v>314.3565255003804</v>
+        <v>314.373929942483</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31387,7 +31516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I695"/>
+  <dimension ref="A1:I698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64047,6 +64176,147 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-43.58030813547121,172.7780785101385</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-43.5811258655461,172.7760661059051</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-43.58177250842403,172.776323524316</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-43.58248859270168,172.77632872893378</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-43.58308419029412,172.77681243544038</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-43.58364081763546,172.77735920411214</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>-43.584145963858056,172.77794428326632</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:34+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>-43.58030769688488,172.77808392640728</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>-43.581126911939776,172.77605318050843</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-43.581773702546336,172.77631691295122</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-43.582493904055205,172.77631124302607</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-43.583090125502615,172.77679812712842</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>-43.583651065709695,172.77734082563995</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>-43.584154452845425,172.7779299916049</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>-43.58030762710975,172.7780847880864</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>-43.58112748994708,172.7760460407653</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>-43.58177509206998,172.77630921972644</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-43.582496091082334,172.77630404294553</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>-43.58309445418737,172.77678769174122</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>-43.58365649115956,172.77733109585805</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>-43.584158440959676,172.77792327740016</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I698"/>
+  <dimension ref="A1:I701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23470,6 +23470,105 @@
         <v>311.98</v>
       </c>
       <c r="I698" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:20+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>494.48</v>
+      </c>
+      <c r="C699" t="n">
+        <v>319.72</v>
+      </c>
+      <c r="D699" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="E699" t="n">
+        <v>301.89</v>
+      </c>
+      <c r="F699" t="n">
+        <v>310.36</v>
+      </c>
+      <c r="G699" t="n">
+        <v>309.06</v>
+      </c>
+      <c r="H699" t="n">
+        <v>310.75</v>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>481.7</v>
+      </c>
+      <c r="C700" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="D700" t="n">
+        <v>331.93</v>
+      </c>
+      <c r="E700" t="n">
+        <v>301.54</v>
+      </c>
+      <c r="F700" t="n">
+        <v>309.05</v>
+      </c>
+      <c r="G700" t="n">
+        <v>308.04</v>
+      </c>
+      <c r="H700" t="n">
+        <v>309.78</v>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>473.01</v>
+      </c>
+      <c r="C701" t="n">
+        <v>319.93</v>
+      </c>
+      <c r="D701" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="E701" t="n">
+        <v>300.94</v>
+      </c>
+      <c r="F701" t="n">
+        <v>308.75</v>
+      </c>
+      <c r="G701" t="n">
+        <v>307.37</v>
+      </c>
+      <c r="H701" t="n">
+        <v>309.21</v>
+      </c>
+      <c r="I701" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23486,7 +23585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B732"/>
+  <dimension ref="A1:B735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30809,6 +30908,36 @@
       </c>
       <c r="B732" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -30977,28 +31106,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.313429301502046</v>
+        <v>1.344103704208314</v>
       </c>
       <c r="J2" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03357212865349779</v>
+        <v>0.03537789956670645</v>
       </c>
       <c r="M2" t="n">
-        <v>44.8953924936915</v>
+        <v>44.83763578203775</v>
       </c>
       <c r="N2" t="n">
-        <v>2711.391150413494</v>
+        <v>2705.168774366772</v>
       </c>
       <c r="O2" t="n">
-        <v>52.07102025516203</v>
+        <v>52.01123700092867</v>
       </c>
       <c r="P2" t="n">
-        <v>413.3433370865405</v>
+        <v>413.0208625535143</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31059,28 +31188,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006354789671600304</v>
+        <v>0.003967657731519395</v>
       </c>
       <c r="J3" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K3" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002219348085752415</v>
+        <v>8.712773200802992e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.371329723824507</v>
+        <v>2.374013493700051</v>
       </c>
       <c r="N3" t="n">
-        <v>10.02627154104604</v>
+        <v>10.01461429606386</v>
       </c>
       <c r="O3" t="n">
-        <v>3.166428830882835</v>
+        <v>3.16458753964302</v>
       </c>
       <c r="P3" t="n">
-        <v>322.42561499942</v>
+        <v>322.4505465225384</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31141,28 +31270,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2783740759581425</v>
+        <v>0.2750436881723297</v>
       </c>
       <c r="J4" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K4" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3036770684876194</v>
+        <v>0.2993826683824108</v>
       </c>
       <c r="M4" t="n">
-        <v>2.195464207642195</v>
+        <v>2.203077932669576</v>
       </c>
       <c r="N4" t="n">
-        <v>9.792987391099503</v>
+        <v>9.813358470169788</v>
       </c>
       <c r="O4" t="n">
-        <v>3.129374920187657</v>
+        <v>3.132628045295162</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8499226392336</v>
+        <v>328.8847095861616</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31223,28 +31352,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01433295926198604</v>
+        <v>0.009330190979181542</v>
       </c>
       <c r="J5" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K5" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006158873719450675</v>
+        <v>0.0002617393797582634</v>
       </c>
       <c r="M5" t="n">
-        <v>3.208128707452136</v>
+        <v>3.217801173197111</v>
       </c>
       <c r="N5" t="n">
-        <v>18.37222661761517</v>
+        <v>18.43140264882316</v>
       </c>
       <c r="O5" t="n">
-        <v>4.286283543772527</v>
+        <v>4.293180947598547</v>
       </c>
       <c r="P5" t="n">
-        <v>306.7741251451115</v>
+        <v>306.8263787060837</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31301,28 +31430,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0475796637183807</v>
+        <v>0.04181825257783371</v>
       </c>
       <c r="J6" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K6" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005457782155647739</v>
+        <v>0.004229502575391453</v>
       </c>
       <c r="M6" t="n">
-        <v>3.446779683162605</v>
+        <v>3.457589314545014</v>
       </c>
       <c r="N6" t="n">
-        <v>22.73571842054839</v>
+        <v>22.82242558394498</v>
       </c>
       <c r="O6" t="n">
-        <v>4.768198655734511</v>
+        <v>4.77728223825482</v>
       </c>
       <c r="P6" t="n">
-        <v>314.6790720319623</v>
+        <v>314.7392510427292</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31379,28 +31508,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04350356330415836</v>
+        <v>0.03749985936780709</v>
       </c>
       <c r="J7" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K7" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00532118665734671</v>
+        <v>0.00395852725022916</v>
       </c>
       <c r="M7" t="n">
-        <v>3.16589491260052</v>
+        <v>3.180732540140554</v>
       </c>
       <c r="N7" t="n">
-        <v>19.49768073333422</v>
+        <v>19.61386296181496</v>
       </c>
       <c r="O7" t="n">
-        <v>4.415617820116934</v>
+        <v>4.428754109432466</v>
       </c>
       <c r="P7" t="n">
-        <v>313.8396298469081</v>
+        <v>313.9023397188491</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31457,28 +31586,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01629240889445184</v>
+        <v>0.01199686162392883</v>
       </c>
       <c r="J8" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K8" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000817145526239349</v>
+        <v>0.0004451331113978219</v>
       </c>
       <c r="M8" t="n">
-        <v>3.066482657404197</v>
+        <v>3.074336366149023</v>
       </c>
       <c r="N8" t="n">
-        <v>17.88854785667815</v>
+        <v>17.91480611604263</v>
       </c>
       <c r="O8" t="n">
-        <v>4.22948553096924</v>
+        <v>4.232588583366288</v>
       </c>
       <c r="P8" t="n">
-        <v>314.373929942483</v>
+        <v>314.4187987486088</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31516,7 +31645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I698"/>
+  <dimension ref="A1:I701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64317,6 +64446,147 @@
         </is>
       </c>
     </row>
+    <row r="699">
+      <c r="A699" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:20+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>-43.58030725829828,172.778089342676</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>-43.581128038057045,172.7760392703191</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>-43.5817747012665,172.77631138344591</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>-43.582500152702956,172.77629067136604</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>-43.58309972000877,172.77677499714449</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>-43.583664547129,172.7773166486029</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>-43.584165448645166,172.77791147958112</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:30+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>-43.58031999714068,172.7779320246575</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>-43.581127788916206,172.77604234779466</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>-43.58177767571414,172.7762949151356</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>-43.58250136771736,172.77628667132052</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>-43.583105565961354,172.77676090398788</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>-43.58367013698427,172.7773066239746</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>-43.584170975030425,172.77790217560806</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>-43.58032865903105,172.77782505329137</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>-43.58112782877875,172.77604185539857</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>-43.581777067798015,172.7762982809218</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>-43.582503450598885,172.77627981409933</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>-43.58310690472888,172.77675767654705</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>-43.58367380875148,172.77730003916872</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>-43.58417422249357,172.77789670832414</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I701"/>
+  <dimension ref="A1:I705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23569,6 +23569,138 @@
         <v>309.21</v>
       </c>
       <c r="I701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:53+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>462.83</v>
+      </c>
+      <c r="C702" t="n">
+        <v>320.78</v>
+      </c>
+      <c r="D702" t="n">
+        <v>334.11</v>
+      </c>
+      <c r="E702" t="n">
+        <v>301.05</v>
+      </c>
+      <c r="F702" t="n">
+        <v>308.77</v>
+      </c>
+      <c r="G702" t="n">
+        <v>307.13</v>
+      </c>
+      <c r="H702" t="n">
+        <v>308.91</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:53+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>452.2</v>
+      </c>
+      <c r="C703" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="D703" t="n">
+        <v>334.44</v>
+      </c>
+      <c r="E703" t="n">
+        <v>300.88</v>
+      </c>
+      <c r="F703" t="n">
+        <v>308.66</v>
+      </c>
+      <c r="G703" t="n">
+        <v>306.72</v>
+      </c>
+      <c r="H703" t="n">
+        <v>308.58</v>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>445.41</v>
+      </c>
+      <c r="C704" t="n">
+        <v>320.79</v>
+      </c>
+      <c r="D704" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="E704" t="n">
+        <v>301.74</v>
+      </c>
+      <c r="F704" t="n">
+        <v>309.67</v>
+      </c>
+      <c r="G704" t="n">
+        <v>307.68</v>
+      </c>
+      <c r="H704" t="n">
+        <v>309.48</v>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>439.02</v>
+      </c>
+      <c r="C705" t="n">
+        <v>321.14</v>
+      </c>
+      <c r="D705" t="n">
+        <v>334.76</v>
+      </c>
+      <c r="E705" t="n">
+        <v>302</v>
+      </c>
+      <c r="F705" t="n">
+        <v>310.15</v>
+      </c>
+      <c r="G705" t="n">
+        <v>307.92</v>
+      </c>
+      <c r="H705" t="n">
+        <v>309.7</v>
+      </c>
+      <c r="I705" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23585,7 +23717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B735"/>
+  <dimension ref="A1:B739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30938,6 +31070,46 @@
       </c>
       <c r="B735" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -31106,28 +31278,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.344103704208314</v>
+        <v>1.345070621059999</v>
       </c>
       <c r="J2" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="K2" t="n">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03537789956670645</v>
+        <v>0.0358826327061007</v>
       </c>
       <c r="M2" t="n">
-        <v>44.83763578203775</v>
+        <v>44.62543885095626</v>
       </c>
       <c r="N2" t="n">
-        <v>2705.168774366772</v>
+        <v>2690.204942937203</v>
       </c>
       <c r="O2" t="n">
-        <v>52.01123700092867</v>
+        <v>51.86718560840951</v>
       </c>
       <c r="P2" t="n">
-        <v>413.0208625535143</v>
+        <v>413.0107558684659</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31188,28 +31360,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003967657731519395</v>
+        <v>0.00180183134526892</v>
       </c>
       <c r="J3" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="K3" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L3" t="n">
-        <v>8.712773200802992e-05</v>
+        <v>1.817434078443814e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.374013493700051</v>
+        <v>2.372176570994558</v>
       </c>
       <c r="N3" t="n">
-        <v>10.01461429606386</v>
+        <v>9.978121021361268</v>
       </c>
       <c r="O3" t="n">
-        <v>3.16458753964302</v>
+        <v>3.158816395639555</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4505465225384</v>
+        <v>322.4732623244068</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31270,28 +31442,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2750436881723297</v>
+        <v>0.2730195054632865</v>
       </c>
       <c r="J4" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="K4" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2993826683824108</v>
+        <v>0.2987130510502369</v>
       </c>
       <c r="M4" t="n">
-        <v>2.203077932669576</v>
+        <v>2.200838013507976</v>
       </c>
       <c r="N4" t="n">
-        <v>9.813358470169788</v>
+        <v>9.774981902586108</v>
       </c>
       <c r="O4" t="n">
-        <v>3.132628045295162</v>
+        <v>3.126496745974015</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8847095861616</v>
+        <v>328.9059376769032</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31352,28 +31524,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009330190979181542</v>
+        <v>0.00277456559430175</v>
       </c>
       <c r="J5" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="K5" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002617393797582634</v>
+        <v>2.323506082457794e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.217801173197111</v>
+        <v>3.230558171521002</v>
       </c>
       <c r="N5" t="n">
-        <v>18.43140264882316</v>
+        <v>18.50645093600574</v>
       </c>
       <c r="O5" t="n">
-        <v>4.293180947598547</v>
+        <v>4.301912474238143</v>
       </c>
       <c r="P5" t="n">
-        <v>306.8263787060837</v>
+        <v>306.8951345859467</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31430,28 +31602,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04181825257783371</v>
+        <v>0.03423294011216223</v>
       </c>
       <c r="J6" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="K6" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004229502575391453</v>
+        <v>0.002846148689890415</v>
       </c>
       <c r="M6" t="n">
-        <v>3.457589314545014</v>
+        <v>3.472297559736556</v>
       </c>
       <c r="N6" t="n">
-        <v>22.82242558394498</v>
+        <v>22.93401215833785</v>
       </c>
       <c r="O6" t="n">
-        <v>4.77728223825482</v>
+        <v>4.788946873618234</v>
       </c>
       <c r="P6" t="n">
-        <v>314.7392510427292</v>
+        <v>314.8188052394682</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31508,28 +31680,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03749985936780709</v>
+        <v>0.02876021481425685</v>
       </c>
       <c r="J7" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="K7" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00395852725022916</v>
+        <v>0.002325601596908977</v>
       </c>
       <c r="M7" t="n">
-        <v>3.180732540140554</v>
+        <v>3.204200828744879</v>
       </c>
       <c r="N7" t="n">
-        <v>19.61386296181496</v>
+        <v>19.82096586738257</v>
       </c>
       <c r="O7" t="n">
-        <v>4.428754109432466</v>
+        <v>4.452074333092672</v>
       </c>
       <c r="P7" t="n">
-        <v>313.9023397188491</v>
+        <v>313.9940037746168</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31586,28 +31758,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01199686162392883</v>
+        <v>0.005543633911176447</v>
       </c>
       <c r="J8" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="K8" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004451331113978219</v>
+        <v>9.542726281197567e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.074336366149023</v>
+        <v>3.088907162957509</v>
       </c>
       <c r="N8" t="n">
-        <v>17.91480611604263</v>
+        <v>17.98714455048717</v>
       </c>
       <c r="O8" t="n">
-        <v>4.232588583366288</v>
+        <v>4.241125387263052</v>
       </c>
       <c r="P8" t="n">
-        <v>314.4187987486088</v>
+        <v>314.4864813535892</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31645,7 +31817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I701"/>
+  <dimension ref="A1:I705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64587,6 +64759,194 @@
         </is>
       </c>
     </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:53+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>-43.580338805974314,172.77769974042124</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>-43.58112698169929,172.7760523188153</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>-43.58177294265036,172.7763211201834</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>-43.58250306873731,172.7762810712566</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>-43.58310681547771,172.77675789170976</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>-43.583675124011265,172.7772976804321</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>-43.58417593168459,172.77789383080602</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:53+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>-43.580349401309604,172.77756888813627</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>-43.58112771915676,172.77604320948782</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>-43.58177222617689,172.77632508700222</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>-43.58250365888702,172.77627912837718</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>-43.58310730635912,172.77675670831476</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>-43.583677370913314,172.77729365092347</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>-43.584177811794625,172.77789066553595</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>-43.58035616908878,172.77748530513847</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>-43.58112697173365,172.77605244191432</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>-43.581771661682524,172.77632821237455</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>-43.58250067342344,172.77628895706084</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>-43.583102799174846,172.7767675740318</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>-43.58367210987416,172.77730308587005</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>-43.58417268422159,172.77789929809026</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>-43.58036253812114,172.7774066460117</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>-43.58112662293595,172.77605675037995</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>-43.58177153141459,172.7763289336143</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>-43.582499770841245,172.77629192852316</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>-43.58310065714631,172.77677273793634</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>-43.58367079461425,172.77730544460644</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>-43.58417143081475,172.77790140827</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
